--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XL/LTAIPT_A63F40B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XL/LTAIPT_A63F40B.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="82">
   <si>
     <t>49009</t>
   </si>
@@ -152,6 +152,114 @@
   </si>
   <si>
     <t>s/n</t>
+  </si>
+  <si>
+    <t>610140AE8B653655BB4C7CFAE94BD57A</t>
+  </si>
+  <si>
+    <t>01/04/2022</t>
+  </si>
+  <si>
+    <t>30/06/2022</t>
+  </si>
+  <si>
+    <t>Sondeo para estudiantes, Fondo de aportación Múltiple 2021</t>
+  </si>
+  <si>
+    <t>http://www.cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202021/Planeacion%20y%20Evaluacion/ENCUESTA%20SATISFACCIÓN%20FAM%2021.pdf</t>
+  </si>
+  <si>
+    <t>15/07/2022</t>
+  </si>
+  <si>
+    <t>En el periodo del 1 de abril de 2022 al 30 de junio de 2022 el Colegio de Bachilleres del Estado de Tlaxcala, no ha  aplicado ninguna encuesta a ningún programa financiado con recursos públicos, por lo que no se cuenta con el hipervínculo correspondiente.</t>
+  </si>
+  <si>
+    <t>A14B23F91FAA1DC76DA9CCE87680E096</t>
+  </si>
+  <si>
+    <t>31/03/2022</t>
+  </si>
+  <si>
+    <t>cualitativa</t>
+  </si>
+  <si>
+    <t>http://www.cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202021/Planeacion%20y%20Evaluacion/ENCUESTA%20SATISFACCIÓN%20FAM%2022.pdf</t>
+  </si>
+  <si>
+    <t>subdireccion de planeacion y evaluacion</t>
+  </si>
+  <si>
+    <t>04/05/2022</t>
+  </si>
+  <si>
+    <t>En el periodo del 1 de enero de 2022 al 31 de marzo de 2022 el Colegio de Bachilleres del Estado de Tlaxcala, no ha  aplicado ninguna encuesta a ningún programa financiado con recursos públicos, por lo que no se cuenta con el hipervínculo correspondiente.</t>
+  </si>
+  <si>
+    <t>06165FFEEB82D2B4</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>01/07/2021</t>
+  </si>
+  <si>
+    <t>30/09/2021</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>26/10/2021</t>
+  </si>
+  <si>
+    <t>En el periodo del 1 de abril de 2021 al 30 de junio de 2021 el Colegio de Bachilleres del Estado de Tlaxcala, no ha  aplicado ninguna encuesta a ningún programa financiado con recursos públicos, por lo que no se cuenta con el hipervínculo correspondiente.</t>
+  </si>
+  <si>
+    <t>AE9C9DB41373D967</t>
+  </si>
+  <si>
+    <t>Sondeo para estudiantes, Fondo de aportación Múltiple 2018</t>
+  </si>
+  <si>
+    <t>http://www.cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202018/Planeacion%20y%20Evaluacion/ENCUESTA%20SATISFACCIÓN%20FAM%202018.pdf</t>
+  </si>
+  <si>
+    <t>En el periodo del 1 de julio de 2021 al 30 de septiembre de 2021 el Colegio de Bachilleres del Estado de Tlaxcala, no ha  aplicado ninguna encuesta a ningún programa financiado con recursos públicos, por lo que no se cuenta con el hipervínculo correspondiente.</t>
+  </si>
+  <si>
+    <t>30F8ACA769F9144B</t>
+  </si>
+  <si>
+    <t>01/04/2021</t>
+  </si>
+  <si>
+    <t>30/06/2021</t>
+  </si>
+  <si>
+    <t>15/07/2021</t>
+  </si>
+  <si>
+    <t>009652012497A6B6</t>
+  </si>
+  <si>
+    <t>922236F5845EF263</t>
+  </si>
+  <si>
+    <t>01/01/2021</t>
+  </si>
+  <si>
+    <t>31/03/2021</t>
+  </si>
+  <si>
+    <t>29/04/2021</t>
+  </si>
+  <si>
+    <t>En el periodo del 1 de enero de 2021 al 31 de marzo de 2021 el Colegio de Bachilleres del Estado de Tlaxcala, no ha  aplicado ninguna encuesta a ningún programa financiado con recursos públicos, por lo que no se cuenta con el hipervínculo correspondiente.</t>
+  </si>
+  <si>
+    <t>719583278CAA8FFF</t>
   </si>
 </sst>
 </file>
@@ -544,10 +652,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -558,7 +666,7 @@
     <col min="9" max="9" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="221.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="221" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
@@ -755,6 +863,310 @@
       </c>
       <c r="L8" s="2" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
